--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356617</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77857</v>
+        <v>77873</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752478</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194717</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356615</v>
+        <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>77857</v>
+        <v>77873</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752473</v>
+        <v>752478</v>
       </c>
       <c r="R9" t="n">
-        <v>7194715</v>
+        <v>7194717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356617</v>
+        <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>77873</v>
+        <v>56781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752478</v>
+        <v>752505</v>
       </c>
       <c r="R9" t="n">
-        <v>7194717</v>
+        <v>7194699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,6 +1577,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356372</v>
+        <v>113356617</v>
       </c>
       <c r="B10" t="n">
-        <v>56781</v>
+        <v>77873</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752505</v>
+        <v>752478</v>
       </c>
       <c r="R10" t="n">
-        <v>7194699</v>
+        <v>7194717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,11 +1688,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B8" t="n">
-        <v>77873</v>
+        <v>56782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,6 +1471,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>77885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752478</v>
       </c>
       <c r="R9" t="n">
-        <v>7194699</v>
+        <v>7194717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356617</v>
+        <v>113356615</v>
       </c>
       <c r="B10" t="n">
-        <v>77873</v>
+        <v>77885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752478</v>
+        <v>752473</v>
       </c>
       <c r="R10" t="n">
-        <v>7194717</v>
+        <v>7194715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>56782</v>
+        <v>77885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,11 +1471,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B10" t="n">
-        <v>77885</v>
+        <v>56782</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R10" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,6 +1683,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77885</v>
+        <v>77907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>77885</v>
+        <v>77907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77907</v>
+        <v>77910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>77907</v>
+        <v>77910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>113356372</v>
       </c>
       <c r="B10" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356617</v>
       </c>
       <c r="B8" t="n">
         <v>77910</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752478</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356617</v>
+        <v>113356615</v>
       </c>
       <c r="B9" t="n">
         <v>77910</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752478</v>
+        <v>752473</v>
       </c>
       <c r="R9" t="n">
-        <v>7194717</v>
+        <v>7194715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356617</v>
+        <v>113356372</v>
       </c>
       <c r="B8" t="n">
-        <v>77910</v>
+        <v>56789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752478</v>
+        <v>752505</v>
       </c>
       <c r="R8" t="n">
-        <v>7194717</v>
+        <v>7194699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,6 +1471,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356615</v>
+        <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>77910</v>
+        <v>77916</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752473</v>
+        <v>752478</v>
       </c>
       <c r="R9" t="n">
-        <v>7194715</v>
+        <v>7194717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B10" t="n">
-        <v>56785</v>
+        <v>77916</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R10" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,11 +1688,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>56789</v>
+        <v>77916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,11 +1471,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356615</v>
+        <v>113356372</v>
       </c>
       <c r="B10" t="n">
-        <v>77916</v>
+        <v>56789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752473</v>
+        <v>752505</v>
       </c>
       <c r="R10" t="n">
-        <v>7194715</v>
+        <v>7194699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,6 +1683,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356615</v>
+        <v>113356617</v>
       </c>
       <c r="B8" t="n">
-        <v>77916</v>
+        <v>77923</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752473</v>
+        <v>752478</v>
       </c>
       <c r="R8" t="n">
-        <v>7194715</v>
+        <v>7194717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356617</v>
+        <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>77916</v>
+        <v>56796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752478</v>
+        <v>752505</v>
       </c>
       <c r="R9" t="n">
-        <v>7194717</v>
+        <v>7194699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,6 +1577,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356372</v>
+        <v>113356615</v>
       </c>
       <c r="B10" t="n">
-        <v>56789</v>
+        <v>77923</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752505</v>
+        <v>752473</v>
       </c>
       <c r="R10" t="n">
-        <v>7194699</v>
+        <v>7194715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,11 +1688,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356617</v>
+        <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77923</v>
+        <v>77925</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752478</v>
+        <v>752473</v>
       </c>
       <c r="R8" t="n">
-        <v>7194717</v>
+        <v>7194715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
         <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356615</v>
+        <v>113356617</v>
       </c>
       <c r="B10" t="n">
-        <v>77923</v>
+        <v>77925</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752473</v>
+        <v>752478</v>
       </c>
       <c r="R10" t="n">
-        <v>7194715</v>
+        <v>7194717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>113356615</v>
       </c>
       <c r="B8" t="n">
-        <v>77925</v>
+        <v>77953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>113356372</v>
       </c>
       <c r="B9" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>113356617</v>
       </c>
       <c r="B10" t="n">
-        <v>77925</v>
+        <v>77953</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113356372</v>
+        <v>113356617</v>
       </c>
       <c r="B9" t="n">
-        <v>56826</v>
+        <v>77953</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752505</v>
+        <v>752478</v>
       </c>
       <c r="R9" t="n">
-        <v>7194699</v>
+        <v>7194717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,11 +1577,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113356617</v>
+        <v>113356372</v>
       </c>
       <c r="B10" t="n">
-        <v>77953</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752478</v>
+        <v>752505</v>
       </c>
       <c r="R10" t="n">
-        <v>7194717</v>
+        <v>7194699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,6 +1683,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 14562-2019 artfynd.xlsx
+++ b/artfynd/A 14562-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
